--- a/output/yearly_surface_area_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_28_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497629433278</v>
+        <v>10.84497637637089</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907180990955</v>
+        <v>37.78907209576948</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.17086515826795</v>
+        <v>5.724570863463152</v>
       </c>
       <c r="C2" t="n">
-        <v>10.9415781638307</v>
+        <v>9.789988106749192</v>
       </c>
       <c r="D2" t="n">
-        <v>29.40923422841745</v>
+        <v>34.45247218513332</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.4841658491097</v>
+        <v>16.50808764691012</v>
       </c>
       <c r="C3" t="n">
-        <v>54.33973543006095</v>
+        <v>29.85494768614551</v>
       </c>
       <c r="D3" t="n">
-        <v>80.93528073810705</v>
+        <v>95.07735641778235</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.14624901686633</v>
+        <v>35.25063306868597</v>
       </c>
       <c r="C4" t="n">
-        <v>96.43511349275569</v>
+        <v>53.89696721544564</v>
       </c>
       <c r="D4" t="n">
-        <v>97.08601222067134</v>
+        <v>111.9035303208684</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.43728830567989</v>
+        <v>45.7248993252952</v>
       </c>
       <c r="C5" t="n">
-        <v>140.5617275555371</v>
+        <v>96.70214886831084</v>
       </c>
       <c r="D5" t="n">
-        <v>69.01686360855078</v>
+        <v>76.18362184955249</v>
       </c>
     </row>
     <row r="6">
@@ -839,10 +839,10 @@
         <v>44.23656980565704</v>
       </c>
       <c r="C6" t="n">
-        <v>162.0934182050782</v>
+        <v>104.6140536168359</v>
       </c>
       <c r="D6" t="n">
-        <v>46.85292743747478</v>
+        <v>48.90576188705487</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.00319158948677</v>
+        <v>30.06307819944583</v>
       </c>
       <c r="C7" t="n">
-        <v>162.7119192587536</v>
+        <v>86.41637817091699</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="C8" t="n">
-        <v>110.485886635936</v>
+        <v>51.98844967838984</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>55.80155776168444</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.71549845441346</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.617525551487173</v>
+        <v>7.695656249389462</v>
       </c>
       <c r="C21" t="n">
-        <v>91.41030661784608</v>
+        <v>94.27178905502089</v>
       </c>
       <c r="D21" t="n">
-        <v>7.617525551487173</v>
+        <v>8.657613280563144</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.234498832594745</v>
+        <v>6.888923640699868</v>
       </c>
       <c r="C2" t="n">
-        <v>7.664504327054848</v>
+        <v>7.746971134211581</v>
       </c>
       <c r="D2" t="n">
-        <v>26.91166806881357</v>
+        <v>38.5817030291954</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.67775007329557</v>
+        <v>17.7745421853885</v>
       </c>
       <c r="C3" t="n">
-        <v>48.38543560380405</v>
+        <v>33.90956570468483</v>
       </c>
       <c r="D3" t="n">
-        <v>83.68417430999813</v>
+        <v>99.18106182153402</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.31292514241003</v>
+        <v>33.06820792214531</v>
       </c>
       <c r="C4" t="n">
-        <v>112.8734970526643</v>
+        <v>63.63492269386975</v>
       </c>
       <c r="D4" t="n">
-        <v>109.5169016518444</v>
+        <v>129.503321414901</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.32777453116076</v>
+        <v>49.43099690882691</v>
       </c>
       <c r="C5" t="n">
-        <v>156.5887588273663</v>
+        <v>97.95387719122553</v>
       </c>
       <c r="D5" t="n">
-        <v>83.84125394267762</v>
+        <v>96.55488671267382</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.69570893607505</v>
+        <v>52.327152636355</v>
       </c>
       <c r="C6" t="n">
-        <v>186.6469282882909</v>
+        <v>126.9134709710979</v>
       </c>
       <c r="D6" t="n">
-        <v>54.66174867705392</v>
+        <v>59.41144407019999</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.22572952318131</v>
+        <v>40.60312155223958</v>
       </c>
       <c r="C7" t="n">
-        <v>192.5354510183632</v>
+        <v>117.5574153496258</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>44.49575119957818</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.94696992843745</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>155.9653490351695</v>
+        <v>80.94509821514951</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.53906160508951</v>
+        <v>10.98281156740907</v>
       </c>
       <c r="C9" t="n">
-        <v>89.08280493565131</v>
+        <v>48.59062087399162</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>45.83780031128358</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.53664044579129</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.77689817511908</v>
+        <v>7.87748035252519</v>
       </c>
       <c r="C21" t="n">
-        <v>99.15545173276827</v>
+        <v>103.3919296268931</v>
       </c>
       <c r="D21" t="n">
-        <v>8.749010447008965</v>
+        <v>9.846850440656487</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.024805734513428</v>
+        <v>8.518624829749573</v>
       </c>
       <c r="C2" t="n">
-        <v>11.43834250217959</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="D2" t="n">
-        <v>23.50500353507714</v>
+        <v>43.23715064273378</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.33690369347268</v>
+        <v>19.85584731839174</v>
       </c>
       <c r="C3" t="n">
-        <v>39.97185777840889</v>
+        <v>31.82826057168159</v>
       </c>
       <c r="D3" t="n">
-        <v>84.15541320803658</v>
+        <v>104.6690314882737</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.65002445786518</v>
+        <v>32.71085175779947</v>
       </c>
       <c r="C4" t="n">
-        <v>115.6047191658789</v>
+        <v>73.14314920950011</v>
       </c>
       <c r="D4" t="n">
-        <v>120.7098072279623</v>
+        <v>145.2780435267387</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.72676500971247</v>
+        <v>49.25919106058372</v>
       </c>
       <c r="C5" t="n">
-        <v>174.4565670446582</v>
+        <v>105.2678975878643</v>
       </c>
       <c r="D5" t="n">
-        <v>96.28490609400595</v>
+        <v>114.6435881634213</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.02780170201773</v>
+        <v>58.36490101747288</v>
       </c>
       <c r="C6" t="n">
-        <v>208.9060939866788</v>
+        <v>138.425444551096</v>
       </c>
       <c r="D6" t="n">
-        <v>63.75862290460487</v>
+        <v>72.8554971321558</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.84940135728529</v>
+        <v>50.30475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>221.4007970186279</v>
+        <v>146.8419676196039</v>
       </c>
       <c r="D7" t="n">
-        <v>46.83132898798135</v>
+        <v>49.58611304609789</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.2069942013426</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="C8" t="n">
-        <v>195.5199640392735</v>
+        <v>112.5721005074605</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.64374875654542</v>
+        <v>16.08593613408398</v>
       </c>
       <c r="C9" t="n">
-        <v>127.578114166873</v>
+        <v>70.55624400880974</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>67.47551971288328</v>
+        <v>44.98367980858886</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.80397892098267</v>
+        <v>35.89465956267188</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.919151980196877</v>
+        <v>8.043303158413853</v>
       </c>
       <c r="C21" t="n">
-        <v>105.9186577351332</v>
+        <v>111.6008313229922</v>
       </c>
       <c r="D21" t="n">
-        <v>8.909045977721487</v>
+        <v>11.05954184281905</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.467173038501239</v>
+        <v>7.669413065576083</v>
       </c>
       <c r="C2" t="n">
-        <v>8.234899743222245</v>
+        <v>4.641703145678919</v>
       </c>
       <c r="D2" t="n">
-        <v>19.77338051123501</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.46515278983052</v>
+        <v>23.40486526924396</v>
       </c>
       <c r="C3" t="n">
-        <v>63.00856765856029</v>
+        <v>45.98997120544183</v>
       </c>
       <c r="D3" t="n">
-        <v>90.64967427162924</v>
+        <v>113.6274792895258</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.73339089726815</v>
+        <v>23.66208316775662</v>
       </c>
       <c r="C4" t="n">
-        <v>145.903416814344</v>
+        <v>93.26995889426397</v>
       </c>
       <c r="D4" t="n">
-        <v>112.7203444108018</v>
+        <v>136.0378341343678</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.92567457858028</v>
+        <v>32.86400439966199</v>
       </c>
       <c r="C5" t="n">
-        <v>124.829220594982</v>
+        <v>82.71224408279379</v>
       </c>
       <c r="D5" t="n">
-        <v>63.05274630525141</v>
+        <v>74.34284490408973</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.7057220351</v>
+        <v>31.23528495831652</v>
       </c>
       <c r="C6" t="n">
-        <v>145.831749231934</v>
+        <v>96.6844774096344</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>32.6440929139107</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3433750167749</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="C7" t="n">
-        <v>137.4996564659913</v>
+        <v>79.17009836587128</v>
       </c>
       <c r="D7" t="n">
-        <v>27.36818075128833</v>
+        <v>29.16477905005999</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>51.98844967838984</v>
       </c>
       <c r="D8" t="n">
-        <v>26.36974333606933</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>51.47499562906875</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>26.95781021091316</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.21538796232432</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>26.25291535926396</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>21.5935407549086</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>8.425358797846126</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
-        <v>6.052474596681584</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.559236338522187</v>
+        <v>4.817435984739099</v>
       </c>
       <c r="C2" t="n">
-        <v>4.220533380557038</v>
+        <v>2.263910205993145</v>
       </c>
       <c r="D2" t="n">
-        <v>13.98205080388307</v>
+        <v>24.27273023979814</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.43217427851362</v>
+        <v>25.42726553999239</v>
       </c>
       <c r="C3" t="n">
-        <v>49.07756773529805</v>
+        <v>32.42712667127215</v>
       </c>
       <c r="D3" t="n">
-        <v>87.49335540247574</v>
+        <v>115.6940582069654</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.22510762837556</v>
+        <v>32.73637719810989</v>
       </c>
       <c r="C4" t="n">
-        <v>156.2029319795973</v>
+        <v>106.1347808107142</v>
       </c>
       <c r="D4" t="n">
-        <v>126.8997265032385</v>
+        <v>158.9852049734327</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.02447124381072</v>
+        <v>36.10377182367646</v>
       </c>
       <c r="C5" t="n">
-        <v>186.532063806894</v>
+        <v>124.8537642875881</v>
       </c>
       <c r="D5" t="n">
-        <v>80.03698158872123</v>
+        <v>96.87395471655404</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.41516577237194</v>
+        <v>36.74976181307086</v>
       </c>
       <c r="C6" t="n">
-        <v>171.4720540237479</v>
+        <v>115.0794841441069</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>41.74096714146165</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="C7" t="n">
-        <v>166.9039819558875</v>
+        <v>103.8433816690021</v>
       </c>
       <c r="D7" t="n">
-        <v>29.94330497952771</v>
+        <v>31.85967649821749</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>122.585927090778</v>
+        <v>69.5126461991954</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>52.25155806312797</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
-        <v>4.814490741626358</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.104106314379167</v>
+        <v>4.444371857125311</v>
       </c>
       <c r="C2" t="n">
-        <v>5.305364593749763</v>
+        <v>5.112942043717388</v>
       </c>
       <c r="D2" t="n">
-        <v>11.12123799370787</v>
+        <v>29.14318060056657</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.54307071136451</v>
+        <v>21.06339699461532</v>
       </c>
       <c r="C3" t="n">
-        <v>33.07017141755381</v>
+        <v>19.95893082733765</v>
       </c>
       <c r="D3" t="n">
-        <v>79.50192908990671</v>
+        <v>109.6612185643687</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.61097553387356</v>
+        <v>40.10046672766521</v>
       </c>
       <c r="C4" t="n">
-        <v>140.0453282631032</v>
+        <v>93.23167073379835</v>
       </c>
       <c r="D4" t="n">
-        <v>138.4882764041678</v>
+        <v>177.2869456760017</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.91495746929158</v>
+        <v>42.26423866782519</v>
       </c>
       <c r="C5" t="n">
-        <v>231.8151766652782</v>
+        <v>159.5340019401067</v>
       </c>
       <c r="D5" t="n">
-        <v>101.2181883078462</v>
+        <v>126.0073178400781</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.74096714146165</v>
+        <v>42.74725853831463</v>
       </c>
       <c r="C6" t="n">
-        <v>225.4092728950677</v>
+        <v>155.5323982975967</v>
       </c>
       <c r="D6" t="n">
-        <v>49.71079500453725</v>
+        <v>58.04288777047993</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.29022177202533</v>
+        <v>29.16477905005999</v>
       </c>
       <c r="C7" t="n">
-        <v>203.9139069105838</v>
+        <v>133.8465732584889</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>164.6439987407113</v>
+        <v>100.3051629428966</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>90.63592980376974</v>
+        <v>59.3515574602409</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>38.29306920414684</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>22.99842171968578</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.42062998577414</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32.49781250597791</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.009056713516474</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.16711809390021</v>
+        <v>2.644828315240907</v>
       </c>
       <c r="C2" t="n">
-        <v>2.645810062945154</v>
+        <v>2.41313585703866</v>
       </c>
       <c r="D2" t="n">
-        <v>7.875580083467912</v>
+        <v>20.33494019806418</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.85232123820225</v>
+        <v>20.58724935805562</v>
       </c>
       <c r="C3" t="n">
-        <v>30.2869166760141</v>
+        <v>21.23520284285851</v>
       </c>
       <c r="D3" t="n">
-        <v>75.5503945803133</v>
+        <v>110.9522167954533</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.10796085640069</v>
+        <v>44.75885958431633</v>
       </c>
       <c r="C4" t="n">
-        <v>135.0040538017959</v>
+        <v>86.74820889495241</v>
       </c>
       <c r="D4" t="n">
-        <v>147.1669261097096</v>
+        <v>190.3432083947801</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.82307409571988</v>
+        <v>44.71860792844222</v>
       </c>
       <c r="C5" t="n">
-        <v>276.7301341345697</v>
+        <v>188.0046853632642</v>
       </c>
       <c r="D5" t="n">
-        <v>103.8934508019187</v>
+        <v>133.3704256219292</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.12082138754715</v>
+        <v>35.46170882509904</v>
       </c>
       <c r="C6" t="n">
-        <v>256.6445578533842</v>
+        <v>185.5601335796897</v>
       </c>
       <c r="D6" t="n">
-        <v>48.50324532831367</v>
+        <v>56.47307319138928</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>9.042878103817369</v>
       </c>
       <c r="C7" t="n">
-        <v>211.2200733255885</v>
+        <v>137.8589761257456</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>111.9879606234336</v>
+        <v>74.18576527141022</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>29.17656002251095</v>
       </c>
       <c r="D9" t="n">
-        <v>30.61874740004951</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>22.91890015564179</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>18.30272245027328</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.10280577150543</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.194427103169874</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27.82272993835461</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.140209995258047</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.481277359259189</v>
+        <v>3.53330998758427</v>
       </c>
       <c r="C2" t="n">
-        <v>4.660356352059609</v>
+        <v>2.492657421082652</v>
       </c>
       <c r="D2" t="n">
-        <v>11.68966991446677</v>
+        <v>20.22694795059703</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.18411090450867</v>
+        <v>15.0354660905399</v>
       </c>
       <c r="C3" t="n">
-        <v>20.67069791291659</v>
+        <v>15.2219981543468</v>
       </c>
       <c r="D3" t="n">
-        <v>66.6852128109646</v>
+        <v>103.2994934408494</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.79790850830795</v>
+        <v>42.18079011296421</v>
       </c>
       <c r="C4" t="n">
-        <v>108.636273961135</v>
+        <v>70.93519862264904</v>
       </c>
       <c r="D4" t="n">
-        <v>149.7832837415274</v>
+        <v>199.6217059476167</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.8979489631499</v>
+        <v>54.48699758569799</v>
       </c>
       <c r="C5" t="n">
-        <v>266.5445017030091</v>
+        <v>174.7265476633261</v>
       </c>
       <c r="D5" t="n">
-        <v>124.8046769023758</v>
+        <v>162.7983130567274</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.66675522656639</v>
+        <v>45.56487444950297</v>
       </c>
       <c r="C6" t="n">
-        <v>332.7201874554696</v>
+        <v>239.336345827513</v>
       </c>
       <c r="D6" t="n">
-        <v>63.07434475474484</v>
+        <v>77.52468921355364</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>19.76258128648829</v>
       </c>
       <c r="C7" t="n">
-        <v>275.0591995419416</v>
+        <v>193.313976947831</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>41.62119392154352</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>174.8247224337507</v>
+        <v>118.3300507928681</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>68.33749419721195</v>
+        <v>52.47343304428775</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>23.77302065833652</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
         <v>23.63361248433346</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
-        <v>3.777765165941727</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.43767954964483</v>
+        <v>2.513274122871834</v>
       </c>
       <c r="C2" t="n">
-        <v>2.876520773443155</v>
+        <v>2.555489274154447</v>
       </c>
       <c r="D2" t="n">
-        <v>8.569675710370408</v>
+        <v>14.80573712774615</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.52004854581033</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="C3" t="n">
-        <v>19.94420461177396</v>
+        <v>12.9590696960579</v>
       </c>
       <c r="D3" t="n">
-        <v>62.88094045700821</v>
+        <v>97.41882469241099</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.51788942841936</v>
+        <v>38.02014334236623</v>
       </c>
       <c r="C4" t="n">
-        <v>88.43288795543994</v>
+        <v>58.84890263566655</v>
       </c>
       <c r="D4" t="n">
-        <v>149.3748766965607</v>
+        <v>206.6412020329814</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.82493978013714</v>
+        <v>59.00303702523332</v>
       </c>
       <c r="C5" t="n">
-        <v>252.407334761855</v>
+        <v>162.5037887454533</v>
       </c>
       <c r="D5" t="n">
-        <v>137.8619213688584</v>
+        <v>182.7523351455438</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.70450360768427</v>
+        <v>53.81646390369741</v>
       </c>
       <c r="C6" t="n">
-        <v>375.064929435043</v>
+        <v>263.9301075665998</v>
       </c>
       <c r="D6" t="n">
-        <v>75.02908654935825</v>
+        <v>95.2354177981661</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.49255961009142</v>
+        <v>17.78632315783946</v>
       </c>
       <c r="C7" t="n">
-        <v>336.3830881400143</v>
+        <v>246.3735133715541</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>46.71155576806323</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>220.7214276072891</v>
+        <v>154.2963779379499</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>71.88749389576842</v>
+        <v>61.57030727183869</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.09302935219197</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.44775906859456</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.661918936840602</v>
+        <v>3.937790041733956</v>
       </c>
       <c r="C2" t="n">
-        <v>12.74406694882784</v>
+        <v>4.750677140850315</v>
       </c>
       <c r="D2" t="n">
-        <v>9.937250262386215</v>
+        <v>18.33512012451343</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.59934912567607</v>
+        <v>11.30482481440202</v>
       </c>
       <c r="C3" t="n">
-        <v>16.01230505626548</v>
+        <v>11.56498795602743</v>
       </c>
       <c r="D3" t="n">
-        <v>56.710656135817</v>
+        <v>88.37692833629787</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.24688600431823</v>
+        <v>32.46836007485052</v>
       </c>
       <c r="C4" t="n">
-        <v>72.18594519785947</v>
+        <v>46.99233561147783</v>
       </c>
       <c r="D4" t="n">
-        <v>146.7202309042773</v>
+        <v>207.0751345182585</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.0212893209865</v>
+        <v>58.78214379177778</v>
       </c>
       <c r="C5" t="n">
-        <v>216.3035629381785</v>
+        <v>139.2118244621977</v>
       </c>
       <c r="D5" t="n">
-        <v>152.2936126212865</v>
+        <v>206.0197557361932</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.80137783523521</v>
+        <v>63.51711296936016</v>
       </c>
       <c r="C6" t="n">
-        <v>385.9328765210552</v>
+        <v>262.6823062345021</v>
       </c>
       <c r="D6" t="n">
-        <v>91.4517621459989</v>
+        <v>119.50716629026</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.84727363096077</v>
+        <v>32.99752208743954</v>
       </c>
       <c r="C7" t="n">
-        <v>412.2594229581376</v>
+        <v>300.7505552143764</v>
       </c>
       <c r="D7" t="n">
-        <v>48.32849423695774</v>
+        <v>56.89227946110266</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>303.0017027002143</v>
+        <v>222.3903987045087</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>137.6734258096429</v>
+        <v>108.496865787132</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6919208139783</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>19.30999559483051</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.22766765639403</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.98419422574081</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.36962016288231</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10.44775906859456</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>25.21226279276234</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>2.479894700927443</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.536476214875263</v>
+        <v>4.739877916103601</v>
       </c>
       <c r="C2" t="n">
-        <v>14.87249597163493</v>
+        <v>4.296127953784042</v>
       </c>
       <c r="D2" t="n">
-        <v>15.26028631481242</v>
+        <v>8.587347169046851</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.704714925199963</v>
+        <v>2.816634163484099</v>
       </c>
       <c r="C2" t="n">
-        <v>7.646832868378405</v>
+        <v>2.697842691270235</v>
       </c>
       <c r="D2" t="n">
-        <v>7.473063524726721</v>
+        <v>13.49510394257666</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.51652246562084</v>
+        <v>15.30053797068654</v>
       </c>
       <c r="C3" t="n">
-        <v>27.57238427377167</v>
+        <v>15.38889526406875</v>
       </c>
       <c r="D3" t="n">
-        <v>61.15797323605505</v>
+        <v>96.05910412202917</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.58018150214342</v>
+        <v>44.82267318509238</v>
       </c>
       <c r="C4" t="n">
-        <v>109.5807152526205</v>
+        <v>70.51402885752717</v>
       </c>
       <c r="D4" t="n">
-        <v>149.3493512562503</v>
+        <v>210.5848825609408</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.54493639578177</v>
+        <v>37.40458753180348</v>
       </c>
       <c r="C5" t="n">
-        <v>324.2958104053277</v>
+        <v>216.4508250938156</v>
       </c>
       <c r="D5" t="n">
-        <v>136.0456881160018</v>
+        <v>184.0286071610646</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.26796036999715</v>
+        <v>20.48809283992669</v>
       </c>
       <c r="C6" t="n">
-        <v>335.8195649577768</v>
+        <v>249.5602664195393</v>
       </c>
       <c r="D6" t="n">
-        <v>71.88945739117695</v>
+        <v>91.12974889900595</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.671155576806323</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>213.0765582343192</v>
+        <v>156.3639386030937</v>
       </c>
       <c r="D7" t="n">
-        <v>29.76364514965055</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>101.4734427109503</v>
+        <v>79.94371555681776</v>
       </c>
       <c r="D8" t="n">
-        <v>23.28214680621311</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>35.61093447614454</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>19.19218587032089</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>19.50241814486289</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.21570675749381</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>15.45958109877452</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>9.980447161373073</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.886199381765381</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.365873098514571</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>1.791689560250429</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.622289175772236</v>
+        <v>7.287513208624073</v>
       </c>
       <c r="C2" t="n">
-        <v>9.622109249322987</v>
+        <v>3.643265730459913</v>
       </c>
       <c r="D2" t="n">
-        <v>15.75410541004857</v>
+        <v>19.53481581910303</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.8819125380499</v>
+        <v>10.07273144557228</v>
       </c>
       <c r="C3" t="n">
-        <v>37.47821860962198</v>
+        <v>10.99557428756428</v>
       </c>
       <c r="D3" t="n">
-        <v>15.95340019401067</v>
+        <v>10.34762080276138</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.930157044278233</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
         <v>27.36523550817559</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39571352354898</v>
+        <v>13.39897755737979</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13050021152114</v>
+        <v>70.14758838863537</v>
       </c>
       <c r="D21" t="n">
-        <v>1.575966296888115</v>
+        <v>1.57635030086821</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.278857405735099</v>
+        <v>5.951354583144164</v>
       </c>
       <c r="C2" t="n">
-        <v>6.269440839320131</v>
+        <v>5.712789891012189</v>
       </c>
       <c r="D2" t="n">
-        <v>16.72407214184442</v>
+        <v>25.00216878405352</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.34319509032566</v>
+        <v>19.07044915499429</v>
       </c>
       <c r="C3" t="n">
-        <v>37.50767104074939</v>
+        <v>13.15051049838602</v>
       </c>
       <c r="D3" t="n">
-        <v>25.32909076956771</v>
+        <v>24.25407703341745</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.11931555602838</v>
+        <v>11.80551614356789</v>
       </c>
       <c r="C4" t="n">
-        <v>57.64920694107695</v>
+        <v>17.29348581030757</v>
       </c>
       <c r="D4" t="n">
-        <v>23.43235420496287</v>
+        <v>20.49692856926491</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.117048960983624</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.20146356801562</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4963,10 +4963,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.292021036517808</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4980,10 +4980,10 @@
         <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43269201310513</v>
+        <v>15.44354909248428</v>
       </c>
       <c r="C21" t="n">
-        <v>86.09817649416546</v>
+        <v>86.15874756859652</v>
       </c>
       <c r="D21" t="n">
-        <v>3.248987792232659</v>
+        <v>3.251273493154585</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.387250563829748</v>
+        <v>5.568472978487908</v>
       </c>
       <c r="C2" t="n">
-        <v>7.946265918173683</v>
+        <v>8.394924619014475</v>
       </c>
       <c r="D2" t="n">
-        <v>28.64248927140069</v>
+        <v>27.78346003018473</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.5907754382451</v>
+        <v>19.94911335029519</v>
       </c>
       <c r="C3" t="n">
-        <v>29.66350688381738</v>
+        <v>18.65811511921063</v>
       </c>
       <c r="D3" t="n">
-        <v>32.82964323001334</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.96686692442964</v>
+        <v>25.92108463522854</v>
       </c>
       <c r="C4" t="n">
-        <v>78.64388159639499</v>
+        <v>26.49540704221292</v>
       </c>
       <c r="D4" t="n">
-        <v>30.86025733529424</v>
+        <v>28.03969618099315</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.98990478551705</v>
+        <v>10.79922474671492</v>
       </c>
       <c r="C5" t="n">
-        <v>62.02191121579226</v>
+        <v>20.469439633546</v>
       </c>
       <c r="D5" t="n">
-        <v>31.34229545807943</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31700669748049</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.43373686329462</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.39663573917827</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.71521514948085</v>
+        <v>16.73955536041207</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1270516543591</v>
+        <v>102.1112876985136</v>
       </c>
       <c r="D21" t="n">
-        <v>4.178803787370213</v>
+        <v>5.021866608123622</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.433392705929348</v>
+        <v>4.998077562320511</v>
       </c>
       <c r="C2" t="n">
-        <v>8.06702088579604</v>
+        <v>4.946044933995431</v>
       </c>
       <c r="D2" t="n">
-        <v>28.39803409304324</v>
+        <v>29.0705312704523</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.67560665143783</v>
+        <v>19.47296571373548</v>
       </c>
       <c r="C3" t="n">
-        <v>30.26237298340793</v>
+        <v>26.6839026014283</v>
       </c>
       <c r="D3" t="n">
-        <v>46.4612101034803</v>
+        <v>51.14905539125883</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.82120841130262</v>
+        <v>32.91505528028281</v>
       </c>
       <c r="C4" t="n">
-        <v>75.45320155759286</v>
+        <v>37.52239725631309</v>
       </c>
       <c r="D4" t="n">
-        <v>39.0411609547829</v>
+        <v>40.11322944782042</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.08427573831176</v>
+        <v>24.69095476180729</v>
       </c>
       <c r="C5" t="n">
-        <v>106.1023831364741</v>
+        <v>36.12831551628263</v>
       </c>
       <c r="D5" t="n">
-        <v>35.22019888985433</v>
+        <v>33.30579086657305</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="C6" t="n">
-        <v>55.94980166502573</v>
+        <v>22.90319219237384</v>
       </c>
       <c r="D6" t="n">
-        <v>37.75605320992383</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.02152865489599</v>
+        <v>18.06852312739711</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7108522412312</v>
+        <v>117.8756032596859</v>
       </c>
       <c r="D21" t="n">
-        <v>6.007176218298664</v>
+        <v>6.883246905675091</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.808240402502383</v>
+        <v>6.184028789050658</v>
       </c>
       <c r="C2" t="n">
-        <v>13.27813769993811</v>
+        <v>7.613453446434014</v>
       </c>
       <c r="D2" t="n">
-        <v>35.37335153171683</v>
+        <v>33.3656774765321</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.86428213710246</v>
+        <v>16.34119053718816</v>
       </c>
       <c r="C3" t="n">
-        <v>28.88301745894116</v>
+        <v>21.03885330200914</v>
       </c>
       <c r="D3" t="n">
-        <v>53.57888095926968</v>
+        <v>58.20291264627215</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.6102715236098</v>
+        <v>25.74240655305561</v>
       </c>
       <c r="C4" t="n">
-        <v>63.04783756673017</v>
+        <v>44.83543590524759</v>
       </c>
       <c r="D4" t="n">
-        <v>44.96306310679967</v>
+        <v>48.39623482855076</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.27371198750239</v>
+        <v>22.72745935331366</v>
       </c>
       <c r="C5" t="n">
-        <v>90.66440048719295</v>
+        <v>40.34983064454391</v>
       </c>
       <c r="D5" t="n">
-        <v>33.23215978875454</v>
+        <v>32.66765485881262</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.6050596854523</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="C6" t="n">
-        <v>76.11588125795947</v>
+        <v>27.6126359296458</v>
       </c>
       <c r="D6" t="n">
-        <v>30.87302005544945</v>
+        <v>31.19503330244241</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>31.91956310817654</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.52187317249857</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.11769621798515</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>19.79694245613693</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.034496701046767</v>
+        <v>7.063398941047217</v>
       </c>
       <c r="C21" t="n">
-        <v>65.94840657231344</v>
+        <v>66.21936507231766</v>
       </c>
       <c r="D21" t="n">
-        <v>4.396560438154229</v>
+        <v>5.297549205785413</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.035204048632643</v>
+        <v>5.034402227377644</v>
       </c>
       <c r="C2" t="n">
-        <v>10.58422199948486</v>
+        <v>3.817035074111599</v>
       </c>
       <c r="D2" t="n">
-        <v>26.36777984066083</v>
+        <v>38.63177216211199</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.64815877344792</v>
+        <v>19.64968030049991</v>
       </c>
       <c r="C3" t="n">
-        <v>43.48651455961247</v>
+        <v>26.75753367924682</v>
       </c>
       <c r="D3" t="n">
-        <v>70.85764055401354</v>
+        <v>72.94385442553801</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.45559735469531</v>
+        <v>29.92857876396402</v>
       </c>
       <c r="C4" t="n">
-        <v>68.06358658772712</v>
+        <v>49.95328668748621</v>
       </c>
       <c r="D4" t="n">
-        <v>61.27381946515618</v>
+        <v>68.66343443502191</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.23215978875454</v>
+        <v>32.00497515844602</v>
       </c>
       <c r="C5" t="n">
-        <v>106.0778394438679</v>
+        <v>66.80793127399546</v>
       </c>
       <c r="D5" t="n">
-        <v>42.43604451606839</v>
+        <v>43.83503499462009</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.0704902127233</v>
+        <v>22.98369550412208</v>
       </c>
       <c r="C6" t="n">
-        <v>114.9184775206104</v>
+        <v>49.46928506929254</v>
       </c>
       <c r="D6" t="n">
-        <v>34.41516577237194</v>
+        <v>34.73717901936489</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49822911213864</v>
+        <v>10.54004335279375</v>
       </c>
       <c r="C7" t="n">
-        <v>75.69667498824607</v>
+        <v>30.9014907388726</v>
       </c>
       <c r="D7" t="n">
         <v>33.47661496711198</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.245250024688684</v>
+        <v>7.287403078765159</v>
       </c>
       <c r="C21" t="n">
-        <v>75.16946900614511</v>
+        <v>75.60680694218853</v>
       </c>
       <c r="D21" t="n">
-        <v>5.433937518516514</v>
+        <v>6.376477693919514</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.91561075516378</v>
+        <v>4.370740779306799</v>
       </c>
       <c r="C2" t="n">
-        <v>17.07357432455628</v>
+        <v>9.735991983015619</v>
       </c>
       <c r="D2" t="n">
-        <v>30.98297579832509</v>
+        <v>36.16660367674825</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.74495088554086</v>
+        <v>18.40286071610646</v>
       </c>
       <c r="C3" t="n">
-        <v>42.06788912697583</v>
+        <v>19.53677931451153</v>
       </c>
       <c r="D3" t="n">
-        <v>75.13806054452964</v>
+        <v>86.9239417340126</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.33845058272045</v>
+        <v>34.58697162061513</v>
       </c>
       <c r="C4" t="n">
-        <v>89.74744813142641</v>
+        <v>60.02307288994574</v>
       </c>
       <c r="D4" t="n">
-        <v>81.83456163519713</v>
+        <v>89.79849901204726</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.42975311921541</v>
+        <v>39.49080140332795</v>
       </c>
       <c r="C5" t="n">
-        <v>116.7298020349458</v>
+        <v>80.77329236690633</v>
       </c>
       <c r="D5" t="n">
-        <v>53.75068680751288</v>
+        <v>58.16855147662353</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.5359207399943</v>
+        <v>33.97239755775664</v>
       </c>
       <c r="C6" t="n">
-        <v>143.134888288368</v>
+        <v>81.18758989809849</v>
       </c>
       <c r="D6" t="n">
-        <v>40.01014593887452</v>
+        <v>41.0164373357275</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>19.76258128648829</v>
       </c>
       <c r="C7" t="n">
-        <v>121.5698182168825</v>
+        <v>53.47874269343649</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>67.09263810822702</v>
+        <v>32.62838495064274</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>31.61718481526852</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.440336477598822</v>
+        <v>7.498570177635702</v>
       </c>
       <c r="C21" t="n">
-        <v>83.70378537298676</v>
+        <v>85.2962357706061</v>
       </c>
       <c r="D21" t="n">
-        <v>6.51029441789897</v>
+        <v>7.498570177635702</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_28_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497637637089</v>
+        <v>10.84497637245257</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907209576948</v>
+        <v>37.78907208211618</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.724570863463152</v>
+        <v>6.410812508731672</v>
       </c>
       <c r="C2" t="n">
-        <v>9.789988106749192</v>
+        <v>12.54280866945725</v>
       </c>
       <c r="D2" t="n">
-        <v>34.45247218513332</v>
+        <v>26.15866757965626</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.50808764691012</v>
+        <v>18.18196748265093</v>
       </c>
       <c r="C3" t="n">
-        <v>29.85494768614551</v>
+        <v>22.03041848329843</v>
       </c>
       <c r="D3" t="n">
-        <v>95.07735641778235</v>
+        <v>91.25344910974103</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.25063306868597</v>
+        <v>36.39927788265474</v>
       </c>
       <c r="C4" t="n">
-        <v>53.89696721544564</v>
+        <v>61.96300635353744</v>
       </c>
       <c r="D4" t="n">
-        <v>111.9035303208684</v>
+        <v>117.8637206333508</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.7248993252952</v>
+        <v>45.0622196249286</v>
       </c>
       <c r="C5" t="n">
-        <v>96.70214886831084</v>
+        <v>106.4950822181728</v>
       </c>
       <c r="D5" t="n">
-        <v>76.18362184955249</v>
+        <v>87.20373982972295</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.23656980565704</v>
+        <v>40.37241084174159</v>
       </c>
       <c r="C6" t="n">
-        <v>104.6140536168359</v>
+        <v>121.6405040515883</v>
       </c>
       <c r="D6" t="n">
-        <v>48.90576188705487</v>
+        <v>54.21898046243861</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.06307819944583</v>
+        <v>26.88908787161589</v>
       </c>
       <c r="C7" t="n">
-        <v>86.41637817091699</v>
+        <v>104.5620209885108</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.18763698469816</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>51.98844967838984</v>
+        <v>67.42643232767094</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.695656249389462</v>
+        <v>7.668476747512542</v>
       </c>
       <c r="C21" t="n">
-        <v>94.27178905502089</v>
+        <v>92.98028056358956</v>
       </c>
       <c r="D21" t="n">
-        <v>8.657613280563144</v>
+        <v>7.668476747512542</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.888923640699868</v>
+        <v>7.740098900281853</v>
       </c>
       <c r="C2" t="n">
-        <v>7.746971134211581</v>
+        <v>13.53044685992954</v>
       </c>
       <c r="D2" t="n">
-        <v>38.5817030291954</v>
+        <v>36.07039240173206</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.7745421853885</v>
+        <v>19.64968030049991</v>
       </c>
       <c r="C3" t="n">
-        <v>33.90956570468483</v>
+        <v>35.36746104549135</v>
       </c>
       <c r="D3" t="n">
-        <v>99.18106182153402</v>
+        <v>90.49750337747099</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.06820792214531</v>
+        <v>35.42931115085889</v>
       </c>
       <c r="C4" t="n">
-        <v>63.63492269386975</v>
+        <v>58.4660210310103</v>
       </c>
       <c r="D4" t="n">
-        <v>129.503321414901</v>
+        <v>133.7533072265854</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.43099690882691</v>
+        <v>49.06284151973436</v>
       </c>
       <c r="C5" t="n">
-        <v>97.95387719122553</v>
+        <v>108.9494514787898</v>
       </c>
       <c r="D5" t="n">
-        <v>96.55488671267382</v>
+        <v>105.1206354322272</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.327152636355</v>
+        <v>49.42903341341842</v>
       </c>
       <c r="C6" t="n">
-        <v>126.9134709710979</v>
+        <v>142.6518684178785</v>
       </c>
       <c r="D6" t="n">
-        <v>59.41144407019999</v>
+        <v>67.09951034215676</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.60312155223958</v>
+        <v>36.4110588551057</v>
       </c>
       <c r="C7" t="n">
-        <v>117.5574153496258</v>
+        <v>138.2182957854999</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49575119957818</v>
+        <v>45.57371017884118</v>
       </c>
     </row>
     <row r="8">
@@ -1175,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.36559536107409</v>
+        <v>21.19593293468863</v>
       </c>
       <c r="C8" t="n">
-        <v>80.94509821514951</v>
+        <v>99.72102305886976</v>
       </c>
       <c r="D8" t="n">
         <v>38.7201294554942</v>
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98281156740907</v>
+        <v>10.53906160508951</v>
       </c>
       <c r="C9" t="n">
-        <v>48.59062087399162</v>
+        <v>59.90624491314035</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>34.87658719336794</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1223,7 +1223,7 @@
         <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.87748035252519</v>
+        <v>7.844522483994726</v>
       </c>
       <c r="C21" t="n">
-        <v>103.3919296268931</v>
+        <v>100.9982269814321</v>
       </c>
       <c r="D21" t="n">
-        <v>9.846850440656487</v>
+        <v>8.825087794494067</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.518624829749573</v>
+        <v>8.105309046261667</v>
       </c>
       <c r="C2" t="n">
-        <v>6.827073535332318</v>
+        <v>9.779188882002478</v>
       </c>
       <c r="D2" t="n">
-        <v>43.23715064273378</v>
+        <v>29.07740350438203</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.85584731839174</v>
+        <v>22.00096605217102</v>
       </c>
       <c r="C3" t="n">
-        <v>31.82826057168159</v>
+        <v>42.82383485924587</v>
       </c>
       <c r="D3" t="n">
-        <v>104.6690314882737</v>
+        <v>95.48478171504479</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.71085175779947</v>
+        <v>35.41654843070368</v>
       </c>
       <c r="C4" t="n">
-        <v>73.14314920950011</v>
+        <v>70.83309686140737</v>
       </c>
       <c r="D4" t="n">
-        <v>145.2780435267387</v>
+        <v>143.0190420592669</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.25919106058372</v>
+        <v>50.36365722786139</v>
       </c>
       <c r="C5" t="n">
-        <v>105.2678975878643</v>
+        <v>107.0595871481147</v>
       </c>
       <c r="D5" t="n">
-        <v>114.6435881634213</v>
+        <v>123.822929198129</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.36490101747288</v>
+        <v>56.59382815901164</v>
       </c>
       <c r="C6" t="n">
-        <v>138.425444551096</v>
+        <v>155.8946632004638</v>
       </c>
       <c r="D6" t="n">
-        <v>72.8554971321558</v>
+        <v>79.69827863075608</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.30475236560656</v>
+        <v>45.27427712904591</v>
       </c>
       <c r="C7" t="n">
-        <v>146.8419676196039</v>
+        <v>165.7661363666654</v>
       </c>
       <c r="D7" t="n">
-        <v>49.58611304609789</v>
+        <v>52.52055693409162</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.87734795689393</v>
+        <v>28.45595720759379</v>
       </c>
       <c r="C8" t="n">
-        <v>112.5721005074605</v>
+        <v>134.185276216454</v>
       </c>
       <c r="D8" t="n">
-        <v>41.47393176590651</v>
+        <v>41.0566889916016</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.08593613408398</v>
+        <v>14.8656237377052</v>
       </c>
       <c r="C9" t="n">
-        <v>70.55624400880974</v>
+        <v>86.86405512405351</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98367980858886</v>
+        <v>51.10487674456772</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.043303158413853</v>
+        <v>8.003874479386791</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6008313229922</v>
+        <v>109.052789781645</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05954184281905</v>
+        <v>10.00484309923349</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.669413065576083</v>
+        <v>7.467173038501239</v>
       </c>
       <c r="C2" t="n">
-        <v>4.641703145678919</v>
+        <v>6.727917017203391</v>
       </c>
       <c r="D2" t="n">
-        <v>35.39298648580176</v>
+        <v>24.17848246019044</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.40486526924396</v>
+        <v>25.47635292520473</v>
       </c>
       <c r="C3" t="n">
-        <v>45.98997120544183</v>
+        <v>58.09001166028377</v>
       </c>
       <c r="D3" t="n">
-        <v>113.6274792895258</v>
+        <v>103.9768993567797</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.66208316775662</v>
+        <v>24.19811741427538</v>
       </c>
       <c r="C4" t="n">
-        <v>93.26995889426397</v>
+        <v>91.5214662330004</v>
       </c>
       <c r="D4" t="n">
-        <v>136.0378341343678</v>
+        <v>137.8629031165626</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.86400439966199</v>
+        <v>31.88225669541517</v>
       </c>
       <c r="C5" t="n">
-        <v>82.71224408279379</v>
+        <v>93.14331344041615</v>
       </c>
       <c r="D5" t="n">
-        <v>74.34284490408973</v>
+        <v>80.89601082993718</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.23528495831652</v>
+        <v>28.09565580013523</v>
       </c>
       <c r="C6" t="n">
-        <v>96.6844774096344</v>
+        <v>109.1624907306114</v>
       </c>
       <c r="D6" t="n">
-        <v>32.6440929139107</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.08008670558751</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>79.17009836587128</v>
+        <v>94.3214106855123</v>
       </c>
       <c r="D7" t="n">
-        <v>29.16477905005999</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>51.98844967838984</v>
+        <v>64.00504157837081</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>38.93905919354123</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.817435984739099</v>
+        <v>4.476769531365456</v>
       </c>
       <c r="C2" t="n">
-        <v>2.263910205993145</v>
+        <v>4.070325981807276</v>
       </c>
       <c r="D2" t="n">
-        <v>24.27273023979814</v>
+        <v>16.97049081561036</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.42726553999239</v>
+        <v>26.48755306057895</v>
       </c>
       <c r="C3" t="n">
-        <v>32.42712667127215</v>
+        <v>43.28034754172064</v>
       </c>
       <c r="D3" t="n">
-        <v>115.6940582069654</v>
+        <v>101.2820019086222</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.73637719810989</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="C4" t="n">
-        <v>106.1347808107142</v>
+        <v>119.101704488406</v>
       </c>
       <c r="D4" t="n">
-        <v>158.9852049734327</v>
+        <v>154.0715577136774</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.10377182367646</v>
+        <v>35.12202411942965</v>
       </c>
       <c r="C5" t="n">
-        <v>124.8537642875881</v>
+        <v>129.0752794158494</v>
       </c>
       <c r="D5" t="n">
-        <v>96.87395471655404</v>
+        <v>102.9607904828843</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.74976181307086</v>
+        <v>33.61013265488955</v>
       </c>
       <c r="C6" t="n">
-        <v>115.0794841441069</v>
+        <v>129.4090736352933</v>
       </c>
       <c r="D6" t="n">
-        <v>41.74096714146165</v>
+        <v>44.92084795551706</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.82246789644735</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="C7" t="n">
-        <v>103.8433816690021</v>
+        <v>120.6116324575376</v>
       </c>
       <c r="D7" t="n">
-        <v>31.85967649821749</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>69.5126461991954</v>
+        <v>83.69890052556181</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>43.93124626963626</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.444371857125311</v>
+        <v>5.012803777884214</v>
       </c>
       <c r="C2" t="n">
-        <v>5.112942043717388</v>
+        <v>5.361324212891832</v>
       </c>
       <c r="D2" t="n">
-        <v>29.14318060056657</v>
+        <v>15.78944832740145</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.06339699461532</v>
+        <v>20.83268628411732</v>
       </c>
       <c r="C3" t="n">
-        <v>19.95893082733765</v>
+        <v>29.07445826126929</v>
       </c>
       <c r="D3" t="n">
-        <v>109.6612185643687</v>
+        <v>92.24010555250908</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.10046672766521</v>
+        <v>42.15526467265379</v>
       </c>
       <c r="C4" t="n">
-        <v>93.23167073379835</v>
+        <v>113.4605821798039</v>
       </c>
       <c r="D4" t="n">
-        <v>177.2869456760017</v>
+        <v>167.2171594735422</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.26423866782519</v>
+        <v>42.43604451606839</v>
       </c>
       <c r="C5" t="n">
-        <v>159.5340019401067</v>
+        <v>172.4439842509523</v>
       </c>
       <c r="D5" t="n">
-        <v>126.0073178400781</v>
+        <v>129.5170658827605</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.74725853831463</v>
+        <v>39.72838434775569</v>
       </c>
       <c r="C6" t="n">
-        <v>155.5323982975967</v>
+        <v>165.756318889623</v>
       </c>
       <c r="D6" t="n">
-        <v>58.04288777047993</v>
+        <v>62.14855666964009</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.16477905005999</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="C7" t="n">
-        <v>133.8465732584889</v>
+        <v>152.0521026860417</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="C8" t="n">
-        <v>100.3051629428966</v>
+        <v>117.4955652442582</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>59.3515574602409</v>
+        <v>68.67030666895162</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>38.29306920414684</v>
+        <v>40.42837046088366</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.644828315240907</v>
+        <v>3.000220984178252</v>
       </c>
       <c r="C2" t="n">
-        <v>2.41313585703866</v>
+        <v>2.561379760379928</v>
       </c>
       <c r="D2" t="n">
-        <v>20.33494019806418</v>
+        <v>11.02600846639593</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.58724935805562</v>
+        <v>21.05357951757285</v>
       </c>
       <c r="C3" t="n">
-        <v>21.23520284285851</v>
+        <v>27.48893571891069</v>
       </c>
       <c r="D3" t="n">
-        <v>110.9522167954533</v>
+        <v>88.78926237208154</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.75885958431633</v>
+        <v>46.18828424169969</v>
       </c>
       <c r="C4" t="n">
-        <v>86.74820889495241</v>
+        <v>109.9891222975871</v>
       </c>
       <c r="D4" t="n">
-        <v>190.3432083947801</v>
+        <v>177.0699794333632</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.71860792844222</v>
+        <v>43.71231653158924</v>
       </c>
       <c r="C5" t="n">
-        <v>188.0046853632642</v>
+        <v>207.1978529812894</v>
       </c>
       <c r="D5" t="n">
-        <v>133.3704256219292</v>
+        <v>136.4383871977005</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.46170882509904</v>
+        <v>32.20132469929539</v>
       </c>
       <c r="C6" t="n">
-        <v>185.5601335796897</v>
+        <v>199.2859482327643</v>
       </c>
       <c r="D6" t="n">
-        <v>56.47307319138928</v>
+        <v>60.13597387593413</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>137.8589761257456</v>
+        <v>157.6215574122339</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>74.18576527141022</v>
+        <v>85.11752595819846</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>29.17656002251095</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.53330998758427</v>
+        <v>3.184789552576653</v>
       </c>
       <c r="C2" t="n">
-        <v>2.492657421082652</v>
+        <v>7.344454575470388</v>
       </c>
       <c r="D2" t="n">
-        <v>20.22694795059703</v>
+        <v>14.78512042595696</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.0354660905399</v>
+        <v>15.91903902436203</v>
       </c>
       <c r="C3" t="n">
-        <v>15.2219981543468</v>
+        <v>18.74156367407161</v>
       </c>
       <c r="D3" t="n">
-        <v>103.2994934408494</v>
+        <v>79.09450379264428</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.18079011296421</v>
+        <v>43.29114676646735</v>
       </c>
       <c r="C4" t="n">
-        <v>70.93519862264904</v>
+        <v>89.95165165390975</v>
       </c>
       <c r="D4" t="n">
-        <v>199.6217059476167</v>
+        <v>179.9415914682851</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.48699758569799</v>
+        <v>54.33973543006097</v>
       </c>
       <c r="C5" t="n">
-        <v>174.7265476633261</v>
+        <v>206.7806102069845</v>
       </c>
       <c r="D5" t="n">
-        <v>162.7983130567274</v>
+        <v>161.6693031968435</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.56487444950297</v>
+        <v>42.54600025894403</v>
       </c>
       <c r="C6" t="n">
-        <v>239.336345827513</v>
+        <v>257.4495909708666</v>
       </c>
       <c r="D6" t="n">
-        <v>77.52468921355364</v>
+        <v>81.91211970383264</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.76258128648829</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>193.313976947831</v>
+        <v>215.0528163629681</v>
       </c>
       <c r="D7" t="n">
-        <v>41.62119392154352</v>
+        <v>41.56130731158447</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>118.3300507928681</v>
+        <v>134.185276216454</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>52.47343304428775</v>
+        <v>57.46562012038278</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
         <v>24.91184799526281</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
+        <v>22.92282714645877</v>
+      </c>
+      <c r="D11" t="n">
         <v>23.81130881880213</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.08946221427348</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.60978849752428</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.513274122871834</v>
+        <v>2.34245002233289</v>
       </c>
       <c r="C2" t="n">
-        <v>2.555489274154447</v>
+        <v>4.854742397500478</v>
       </c>
       <c r="D2" t="n">
-        <v>14.80573712774615</v>
+        <v>12.14912784005428</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.9113649691773</v>
+        <v>13.96045235438964</v>
       </c>
       <c r="C3" t="n">
-        <v>12.9590696960579</v>
+        <v>23.53740120931728</v>
       </c>
       <c r="D3" t="n">
-        <v>97.41882469241099</v>
+        <v>74.92698478811657</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.02014334236623</v>
+        <v>39.36022895866312</v>
       </c>
       <c r="C4" t="n">
-        <v>58.84890263566655</v>
+        <v>74.44494666533139</v>
       </c>
       <c r="D4" t="n">
-        <v>206.6412020329814</v>
+        <v>179.4055572217664</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.00303702523332</v>
+        <v>59.07666810305183</v>
       </c>
       <c r="C5" t="n">
-        <v>162.5037887454533</v>
+        <v>196.7422399310609</v>
       </c>
       <c r="D5" t="n">
-        <v>182.7523351455438</v>
+        <v>179.3162181806799</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.81646390369741</v>
+        <v>50.15356321915257</v>
       </c>
       <c r="C6" t="n">
-        <v>263.9301075665998</v>
+        <v>292.6697898607209</v>
       </c>
       <c r="D6" t="n">
-        <v>95.2354177981661</v>
+        <v>96.60397409788615</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.78632315783946</v>
+        <v>15.69029180927252</v>
       </c>
       <c r="C7" t="n">
-        <v>246.3735133715541</v>
+        <v>269.1903117659542</v>
       </c>
       <c r="D7" t="n">
-        <v>46.71155576806323</v>
+        <v>46.95110220789945</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>154.2963779379499</v>
+        <v>172.8219571170873</v>
       </c>
       <c r="D8" t="n">
         <v>34.46425315758427</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>61.57030727183869</v>
+        <v>65.23124446097505</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.937790041733956</v>
+        <v>3.086614782151972</v>
       </c>
       <c r="C2" t="n">
-        <v>4.750677140850315</v>
+        <v>7.780350556155972</v>
       </c>
       <c r="D2" t="n">
-        <v>18.33512012451343</v>
+        <v>11.61603883664826</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.30482481440202</v>
+        <v>11.10356653503143</v>
       </c>
       <c r="C3" t="n">
-        <v>11.56498795602743</v>
+        <v>21.22538536581604</v>
       </c>
       <c r="D3" t="n">
-        <v>88.37692833629787</v>
+        <v>69.14449081010285</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.46836007485052</v>
+        <v>33.61700488881928</v>
       </c>
       <c r="C4" t="n">
-        <v>46.99233561147783</v>
+        <v>67.42545057996669</v>
       </c>
       <c r="D4" t="n">
-        <v>207.0751345182585</v>
+        <v>174.2877064395278</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.78214379177778</v>
+        <v>58.83123117699012</v>
       </c>
       <c r="C5" t="n">
-        <v>139.2118244621977</v>
+        <v>171.5604113171301</v>
       </c>
       <c r="D5" t="n">
-        <v>206.0197557361932</v>
+        <v>196.1286476159066</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.51711296936016</v>
+        <v>60.65924540229769</v>
       </c>
       <c r="C6" t="n">
-        <v>262.6823062345021</v>
+        <v>301.4849024971531</v>
       </c>
       <c r="D6" t="n">
-        <v>119.50716629026</v>
+        <v>119.9901861607494</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.99752208743954</v>
+        <v>29.58398531977338</v>
       </c>
       <c r="C7" t="n">
-        <v>300.7505552143764</v>
+        <v>329.3164681648458</v>
       </c>
       <c r="D7" t="n">
-        <v>56.89227946110266</v>
+        <v>57.85046522044755</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>222.3903987045087</v>
+        <v>243.7532287489193</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>108.496865787132</v>
+        <v>117.3718650335231</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>45.41074005993622</v>
+        <v>45.98015372839937</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>24.52209415667683</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.739877916103601</v>
+        <v>5.546874528994478</v>
       </c>
       <c r="C2" t="n">
-        <v>4.296127953784042</v>
+        <v>6.598326320242812</v>
       </c>
       <c r="D2" t="n">
-        <v>8.587347169046851</v>
+        <v>18.25559856046944</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.816634163484099</v>
+        <v>2.233476027161494</v>
       </c>
       <c r="C2" t="n">
-        <v>2.697842691270235</v>
+        <v>4.544510122958485</v>
       </c>
       <c r="D2" t="n">
-        <v>13.49510394257666</v>
+        <v>8.642325040484671</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.30053797068654</v>
+        <v>14.98637870532756</v>
       </c>
       <c r="C3" t="n">
-        <v>15.38889526406875</v>
+        <v>26.94406574305371</v>
       </c>
       <c r="D3" t="n">
-        <v>96.05910412202917</v>
+        <v>74.13176914767665</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.82267318509238</v>
+        <v>45.16726662928301</v>
       </c>
       <c r="C4" t="n">
-        <v>70.51402885752717</v>
+        <v>98.60477591914113</v>
       </c>
       <c r="D4" t="n">
-        <v>210.5848825609408</v>
+        <v>180.0692186698372</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.40458753180348</v>
+        <v>35.2447425824605</v>
       </c>
       <c r="C5" t="n">
-        <v>216.4508250938156</v>
+        <v>254.6162670964103</v>
       </c>
       <c r="D5" t="n">
-        <v>184.0286071610646</v>
+        <v>177.7699655464912</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.48809283992669</v>
+        <v>18.35475507859837</v>
       </c>
       <c r="C6" t="n">
-        <v>249.5602664195393</v>
+        <v>273.0269817941507</v>
       </c>
       <c r="D6" t="n">
-        <v>91.12974889900595</v>
+        <v>90.76748399613888</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>156.3639386030937</v>
+        <v>171.3954777028166</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>79.94371555681776</v>
+        <v>86.45270283597411</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
         <v>19.21771131063132</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.287513208624073</v>
+        <v>6.191882770684633</v>
       </c>
       <c r="C2" t="n">
-        <v>3.643265730459913</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="D2" t="n">
-        <v>19.53481581910303</v>
+        <v>22.04907168967911</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.07273144557228</v>
+        <v>11.78588118948296</v>
       </c>
       <c r="C3" t="n">
-        <v>10.99557428756428</v>
+        <v>16.62589737141974</v>
       </c>
       <c r="D3" t="n">
-        <v>10.34762080276138</v>
+        <v>18.47158305540374</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39897755737979</v>
+        <v>13.39678486363605</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14758838863537</v>
+        <v>70.13610899197695</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57635030086821</v>
+        <v>1.576092336898359</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.951354583144164</v>
+        <v>4.415901173702153</v>
       </c>
       <c r="C2" t="n">
-        <v>5.712789891012189</v>
+        <v>4.675082567623311</v>
       </c>
       <c r="D2" t="n">
-        <v>25.00216878405352</v>
+        <v>22.62437584436775</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.07044915499429</v>
+        <v>17.54874021341174</v>
       </c>
       <c r="C3" t="n">
-        <v>13.15051049838602</v>
+        <v>20.54307071136451</v>
       </c>
       <c r="D3" t="n">
-        <v>24.25407703341745</v>
+        <v>32.52530144169683</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.80551614356789</v>
+        <v>13.74544960715959</v>
       </c>
       <c r="C4" t="n">
-        <v>17.29348581030757</v>
+        <v>25.89555919491812</v>
       </c>
       <c r="D4" t="n">
-        <v>20.49692856926491</v>
+        <v>24.74691438094935</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44354909248428</v>
+        <v>15.43753928424102</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15874756859652</v>
+        <v>86.12521916471304</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251273493154585</v>
+        <v>3.25000827036653</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.568472978487908</v>
+        <v>4.713370728088937</v>
       </c>
       <c r="C2" t="n">
-        <v>8.394924619014475</v>
+        <v>9.037969365296137</v>
       </c>
       <c r="D2" t="n">
-        <v>27.78346003018473</v>
+        <v>34.7185258129842</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.94911335029519</v>
+        <v>16.27737693641212</v>
       </c>
       <c r="C3" t="n">
-        <v>18.65811511921063</v>
+        <v>19.1146278016854</v>
       </c>
       <c r="D3" t="n">
-        <v>38.62686342359076</v>
+        <v>43.07418052382881</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.92108463522854</v>
+        <v>25.24466046700248</v>
       </c>
       <c r="C4" t="n">
-        <v>26.49540704221292</v>
+        <v>40.93004353775377</v>
       </c>
       <c r="D4" t="n">
-        <v>28.03969618099315</v>
+        <v>35.46759931132452</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.79922474671492</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C5" t="n">
-        <v>20.469439633546</v>
+        <v>29.62423697564751</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>31.53864499892879</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.01453059358123</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73955536041207</v>
+        <v>16.728789774221</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1112876985136</v>
+        <v>102.0456176227481</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021866608123622</v>
+        <v>4.182197443555249</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.998077562320511</v>
+        <v>6.898741117742336</v>
       </c>
       <c r="C2" t="n">
-        <v>4.946044933995431</v>
+        <v>7.073492209098268</v>
       </c>
       <c r="D2" t="n">
-        <v>29.0705312704523</v>
+        <v>33.30186387575606</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.47296571373548</v>
+        <v>16.1595672119025</v>
       </c>
       <c r="C3" t="n">
-        <v>26.6839026014283</v>
+        <v>28.31851252899925</v>
       </c>
       <c r="D3" t="n">
-        <v>51.14905539125883</v>
+        <v>59.87679248201297</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.91505528028281</v>
+        <v>28.4098150654942</v>
       </c>
       <c r="C4" t="n">
-        <v>37.52239725631309</v>
+        <v>44.78438502462675</v>
       </c>
       <c r="D4" t="n">
-        <v>40.11322944782042</v>
+        <v>48.34518394792993</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.69095476180729</v>
+        <v>24.98547907308133</v>
       </c>
       <c r="C5" t="n">
-        <v>36.12831551628263</v>
+        <v>54.43791020048565</v>
       </c>
       <c r="D5" t="n">
-        <v>33.30579086657305</v>
+        <v>36.59464567579986</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.30442390377452</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>22.90319219237384</v>
+        <v>30.10823859384119</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06852312739711</v>
+        <v>18.04964252707871</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8756032596859</v>
+        <v>117.7524298195135</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883246905675091</v>
+        <v>6.016547509026237</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.184028789050658</v>
+        <v>6.404922022506191</v>
       </c>
       <c r="C2" t="n">
-        <v>7.613453446434014</v>
+        <v>6.959609475405639</v>
       </c>
       <c r="D2" t="n">
-        <v>33.3656774765321</v>
+        <v>31.67019919129786</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.34119053718816</v>
+        <v>18.13778883595982</v>
       </c>
       <c r="C3" t="n">
-        <v>21.03885330200914</v>
+        <v>26.10958019444392</v>
       </c>
       <c r="D3" t="n">
-        <v>58.20291264627215</v>
+        <v>67.61296439147783</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.74240655305561</v>
+        <v>21.86253962587222</v>
       </c>
       <c r="C4" t="n">
-        <v>44.83543590524759</v>
+        <v>49.07265899677682</v>
       </c>
       <c r="D4" t="n">
-        <v>48.39623482855076</v>
+        <v>57.99380038526758</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.72745935331366</v>
+        <v>20.59215809657685</v>
       </c>
       <c r="C5" t="n">
-        <v>40.34983064454391</v>
+        <v>51.71356032120075</v>
       </c>
       <c r="D5" t="n">
-        <v>32.66765485881262</v>
+        <v>36.32466505713199</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="C6" t="n">
-        <v>27.6126359296458</v>
+        <v>39.7686360036298</v>
       </c>
       <c r="D6" t="n">
-        <v>31.19503330244241</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>17.6066633279623</v>
+        <v>20.90042687571034</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.063398941047217</v>
+        <v>7.052230461610416</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21936507231766</v>
+        <v>66.11466057759765</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297549205785413</v>
+        <v>4.40764403850651</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.034402227377644</v>
+        <v>5.432991795301848</v>
       </c>
       <c r="C2" t="n">
-        <v>3.817035074111599</v>
+        <v>5.936628367580462</v>
       </c>
       <c r="D2" t="n">
-        <v>38.63177216211199</v>
+        <v>32.78939157413922</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.64968030049991</v>
+        <v>20.73942025221387</v>
       </c>
       <c r="C3" t="n">
-        <v>26.75753367924682</v>
+        <v>26.81152980298039</v>
       </c>
       <c r="D3" t="n">
-        <v>72.94385442553801</v>
+        <v>77.87713663937824</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.92857876396402</v>
+        <v>30.01791780505048</v>
       </c>
       <c r="C4" t="n">
-        <v>49.95328668748621</v>
+        <v>59.42322504265093</v>
       </c>
       <c r="D4" t="n">
-        <v>68.66343443502191</v>
+        <v>79.42240752586271</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.00497515844602</v>
+        <v>27.95526587842793</v>
       </c>
       <c r="C5" t="n">
-        <v>66.80793127399546</v>
+        <v>75.59457322700442</v>
       </c>
       <c r="D5" t="n">
-        <v>43.83503499462009</v>
+        <v>50.36365722786139</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.98369550412208</v>
+        <v>21.25287430153496</v>
       </c>
       <c r="C6" t="n">
-        <v>49.46928506929254</v>
+        <v>64.76491430145784</v>
       </c>
       <c r="D6" t="n">
-        <v>34.73717901936489</v>
+        <v>36.95102009244145</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.54004335279375</v>
+        <v>10.59992996275281</v>
       </c>
       <c r="C7" t="n">
-        <v>30.9014907388726</v>
+        <v>42.22006002113408</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>21.86352137357647</v>
+        <v>24.11663235482289</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.287403078765159</v>
+        <v>7.271525211294918</v>
       </c>
       <c r="C21" t="n">
-        <v>75.60680694218853</v>
+        <v>75.44207406718478</v>
       </c>
       <c r="D21" t="n">
-        <v>6.376477693919514</v>
+        <v>5.453643908471189</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.370740779306799</v>
+        <v>4.903829782712818</v>
       </c>
       <c r="C2" t="n">
-        <v>9.735991983015619</v>
+        <v>5.160065933521236</v>
       </c>
       <c r="D2" t="n">
-        <v>36.16660367674825</v>
+        <v>32.6735453450381</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.40286071610646</v>
+        <v>19.61531913085127</v>
       </c>
       <c r="C3" t="n">
-        <v>19.53677931451153</v>
+        <v>24.58296251434013</v>
       </c>
       <c r="D3" t="n">
-        <v>86.9239417340126</v>
+        <v>86.04036880019046</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.58697162061513</v>
+        <v>35.5952265128766</v>
       </c>
       <c r="C4" t="n">
-        <v>60.02307288994574</v>
+        <v>63.90293981712914</v>
       </c>
       <c r="D4" t="n">
-        <v>89.79849901204726</v>
+        <v>100.6340484238193</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.49080140332795</v>
+        <v>37.3064127613788</v>
       </c>
       <c r="C5" t="n">
-        <v>80.77329236690633</v>
+        <v>94.07597375945062</v>
       </c>
       <c r="D5" t="n">
-        <v>58.16855147662353</v>
+        <v>67.49515466696822</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.97239755775664</v>
+        <v>30.02773528209295</v>
       </c>
       <c r="C6" t="n">
-        <v>81.18758989809849</v>
+        <v>95.27566945404023</v>
       </c>
       <c r="D6" t="n">
-        <v>41.0164373357275</v>
+        <v>43.9548082145382</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.76258128648829</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>53.47874269343649</v>
+        <v>70.30688009193108</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>32.62838495064274</v>
+        <v>41.39048321104552</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>27.17968519207294</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.498570177635702</v>
+        <v>7.47731988187285</v>
       </c>
       <c r="C21" t="n">
-        <v>85.2962357706061</v>
+        <v>84.11984867106956</v>
       </c>
       <c r="D21" t="n">
-        <v>7.498570177635702</v>
+        <v>6.542654896638743</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_28_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497637245257</v>
+        <v>10.8449763055844</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907208211618</v>
+        <v>37.78907184911557</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.410812508731672</v>
+        <v>1.395063487734718</v>
       </c>
       <c r="C2" t="n">
-        <v>12.54280866945725</v>
+        <v>1.657190124768616</v>
       </c>
       <c r="D2" t="n">
-        <v>26.15866757965626</v>
+        <v>21.30883392067702</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.18196748265093</v>
+        <v>10.73541114593887</v>
       </c>
       <c r="C3" t="n">
-        <v>22.03041848329843</v>
+        <v>21.70644174089698</v>
       </c>
       <c r="D3" t="n">
-        <v>91.25344910974103</v>
+        <v>83.9688811442297</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.39927788265474</v>
+        <v>17.67636741496382</v>
       </c>
       <c r="C4" t="n">
-        <v>61.96300635353744</v>
+        <v>78.59283071577416</v>
       </c>
       <c r="D4" t="n">
-        <v>117.8637206333508</v>
+        <v>78.97571232043042</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.0622196249286</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C5" t="n">
-        <v>106.4950822181728</v>
+        <v>101.2181883078462</v>
       </c>
       <c r="D5" t="n">
-        <v>87.20373982972295</v>
+        <v>47.83565688942584</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.37241084174159</v>
+        <v>11.87423848286517</v>
       </c>
       <c r="C6" t="n">
-        <v>121.6405040515883</v>
+        <v>65.77120569831082</v>
       </c>
       <c r="D6" t="n">
-        <v>54.21898046243861</v>
+        <v>29.66547037922588</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.88908787161589</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>104.5620209885108</v>
+        <v>37.36924461445059</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>67.42643232767094</v>
+        <v>28.78975142703771</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.668476747512542</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.98028056358956</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.668476747512542</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.740098900281853</v>
+        <v>1.151590057081509</v>
       </c>
       <c r="C2" t="n">
-        <v>13.53044685992954</v>
+        <v>5.596943661911066</v>
       </c>
       <c r="D2" t="n">
-        <v>36.07039240173206</v>
+        <v>19.38853541117026</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.64968030049991</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="C3" t="n">
-        <v>35.36746104549135</v>
+        <v>12.65963664626262</v>
       </c>
       <c r="D3" t="n">
-        <v>90.49750337747099</v>
+        <v>82.33917995517999</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.42931115085889</v>
+        <v>19.60353815840031</v>
       </c>
       <c r="C4" t="n">
-        <v>58.4660210310103</v>
+        <v>65.37065263497811</v>
       </c>
       <c r="D4" t="n">
-        <v>133.7533072265854</v>
+        <v>101.9868967602714</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.06284151973436</v>
+        <v>21.99114857512856</v>
       </c>
       <c r="C5" t="n">
-        <v>108.9494514787898</v>
+        <v>125.4673566027424</v>
       </c>
       <c r="D5" t="n">
-        <v>105.1206354322272</v>
+        <v>64.35356201337844</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.42903341341842</v>
+        <v>17.42896699349363</v>
       </c>
       <c r="C6" t="n">
-        <v>142.6518684178785</v>
+        <v>116.6492987231975</v>
       </c>
       <c r="D6" t="n">
-        <v>67.09951034215676</v>
+        <v>37.19253002768617</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.4110588551057</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>138.2182957854999</v>
+        <v>67.3125495939783</v>
       </c>
       <c r="D7" t="n">
-        <v>45.57371017884118</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.19593293468863</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>99.72102305886976</v>
+        <v>40.05530633326986</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.53906160508951</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>59.90624491314035</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>37.72365553568369</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.844522483994726</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9982269814321</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.825087794494067</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.105309046261667</v>
+        <v>0.6047565858160352</v>
       </c>
       <c r="C2" t="n">
-        <v>9.779188882002478</v>
+        <v>2.248202242725196</v>
       </c>
       <c r="D2" t="n">
-        <v>29.07740350438203</v>
+        <v>13.0808064113845</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.00096605217102</v>
+        <v>6.739697989654353</v>
       </c>
       <c r="C3" t="n">
-        <v>42.82383485924587</v>
+        <v>18.24087234490574</v>
       </c>
       <c r="D3" t="n">
-        <v>95.48478171504479</v>
+        <v>81.9661158275662</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.41654843070368</v>
+        <v>21.50518346152638</v>
       </c>
       <c r="C4" t="n">
-        <v>70.83309686140737</v>
+        <v>57.82788502324987</v>
       </c>
       <c r="D4" t="n">
-        <v>143.0190420592669</v>
+        <v>116.6895503790716</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.36365722786139</v>
+        <v>22.38384765682728</v>
       </c>
       <c r="C5" t="n">
-        <v>107.0595871481147</v>
+        <v>139.7763293921396</v>
       </c>
       <c r="D5" t="n">
-        <v>123.822929198129</v>
+        <v>75.05461198966867</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.59382815901164</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="C6" t="n">
-        <v>155.8946632004638</v>
+        <v>151.5072327101848</v>
       </c>
       <c r="D6" t="n">
-        <v>79.69827863075608</v>
+        <v>37.91705983342032</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.27427712904591</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>165.7661363666654</v>
+        <v>66.53402366451058</v>
       </c>
       <c r="D7" t="n">
-        <v>52.52055693409162</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.45595720759379</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>134.185276216454</v>
+        <v>40.22220344299182</v>
       </c>
       <c r="D8" t="n">
-        <v>41.0566889916016</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8656237377052</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>86.86405512405351</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>51.10487674456772</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.003874479386791</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.052789781645</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00484309923349</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.467173038501239</v>
+        <v>0.5193445355465627</v>
       </c>
       <c r="C2" t="n">
-        <v>6.727917017203391</v>
+        <v>2.641883072128167</v>
       </c>
       <c r="D2" t="n">
-        <v>24.17848246019044</v>
+        <v>15.83264522638831</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.47635292520473</v>
+        <v>4.295146206079795</v>
       </c>
       <c r="C3" t="n">
-        <v>58.09001166028377</v>
+        <v>12.82653375598458</v>
       </c>
       <c r="D3" t="n">
-        <v>103.9768993567797</v>
+        <v>73.67525646520188</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.19811741427538</v>
+        <v>17.52321477310132</v>
       </c>
       <c r="C4" t="n">
-        <v>91.5214662330004</v>
+        <v>51.5869148673529</v>
       </c>
       <c r="D4" t="n">
-        <v>137.8629031165626</v>
+        <v>130.728542549801</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.88225669541517</v>
+        <v>27.46439202630453</v>
       </c>
       <c r="C5" t="n">
-        <v>93.14331344041615</v>
+        <v>123.6511233498858</v>
       </c>
       <c r="D5" t="n">
-        <v>80.89601082993718</v>
+        <v>99.27923659195872</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.09565580013523</v>
+        <v>21.37362926915731</v>
       </c>
       <c r="C6" t="n">
-        <v>109.1624907306114</v>
+        <v>188.6997627378709</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>50.47557646614552</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>94.3214106855123</v>
+        <v>140.9730798436165</v>
       </c>
       <c r="D7" t="n">
-        <v>28.86534600026472</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>64.00504157837081</v>
+        <v>63.50435024920493</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.476769531365456</v>
+        <v>0.3112140222462389</v>
       </c>
       <c r="C2" t="n">
-        <v>4.070325981807276</v>
+        <v>1.580613803837365</v>
       </c>
       <c r="D2" t="n">
-        <v>16.97049081561036</v>
+        <v>11.3421312271634</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.48755306057895</v>
+        <v>3.175953823238432</v>
       </c>
       <c r="C3" t="n">
-        <v>43.28034754172064</v>
+        <v>11.75642875835555</v>
       </c>
       <c r="D3" t="n">
-        <v>101.2820019086222</v>
+        <v>70.8085531688012</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.28066633689012</v>
+        <v>14.11556849166064</v>
       </c>
       <c r="C4" t="n">
-        <v>119.101704488406</v>
+        <v>43.24009588584652</v>
       </c>
       <c r="D4" t="n">
-        <v>154.0715577136774</v>
+        <v>137.3523943103543</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.12202411942965</v>
+        <v>28.86338250485623</v>
       </c>
       <c r="C5" t="n">
-        <v>129.0752794158494</v>
+        <v>115.2571804785756</v>
       </c>
       <c r="D5" t="n">
-        <v>102.9607904828843</v>
+        <v>118.5951226730147</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.61013265488955</v>
+        <v>26.60634453279281</v>
       </c>
       <c r="C6" t="n">
-        <v>129.4090736352933</v>
+        <v>203.5123720995468</v>
       </c>
       <c r="D6" t="n">
-        <v>44.92084795551706</v>
+        <v>62.67182819600364</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.6066633279623</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>120.6116324575376</v>
+        <v>193.0145438980357</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>83.69890052556181</v>
+        <v>97.71825774220626</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>43.93124626963626</v>
+        <v>49.58905828921062</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.012803777884214</v>
+        <v>0.6135923151542565</v>
       </c>
       <c r="C2" t="n">
-        <v>5.361324212891832</v>
+        <v>7.897178532961342</v>
       </c>
       <c r="D2" t="n">
-        <v>15.78944832740145</v>
+        <v>12.8206432697591</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.83268628411732</v>
+        <v>2.100940087088174</v>
       </c>
       <c r="C3" t="n">
-        <v>29.07445826126929</v>
+        <v>8.767006998924016</v>
       </c>
       <c r="D3" t="n">
-        <v>92.24010555250908</v>
+        <v>63.90195806942489</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.15526467265379</v>
+        <v>10.159125243546</v>
       </c>
       <c r="C4" t="n">
-        <v>113.4605821798039</v>
+        <v>36.00363355784328</v>
       </c>
       <c r="D4" t="n">
-        <v>167.2171594735422</v>
+        <v>141.2450239576929</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.43604451606839</v>
+        <v>26.04085785514665</v>
       </c>
       <c r="C5" t="n">
-        <v>172.4439842509523</v>
+        <v>97.43845964649596</v>
       </c>
       <c r="D5" t="n">
-        <v>129.5170658827605</v>
+        <v>138.7209506100743</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.72838434775569</v>
+        <v>32.40258297866598</v>
       </c>
       <c r="C6" t="n">
-        <v>165.756318889623</v>
+        <v>196.7903455685689</v>
       </c>
       <c r="D6" t="n">
-        <v>62.14855666964009</v>
+        <v>82.07312632732911</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.4698816019025</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="C7" t="n">
-        <v>152.0521026860417</v>
+        <v>243.1995230437241</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>48.20872101703962</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>7.176575718044183</v>
       </c>
       <c r="C8" t="n">
-        <v>117.4955652442582</v>
+        <v>169.0667721483432</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>68.67030666895162</v>
+        <v>80.6515556515797</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>43.15468383557703</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>40.42837046088366</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.000220984178252</v>
+        <v>0.4025165587411922</v>
       </c>
       <c r="C2" t="n">
-        <v>2.561379760379928</v>
+        <v>3.980986940720816</v>
       </c>
       <c r="D2" t="n">
-        <v>11.02600846639593</v>
+        <v>9.230391915328511</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.05357951757285</v>
+        <v>3.259402378099411</v>
       </c>
       <c r="C3" t="n">
-        <v>27.48893571891069</v>
+        <v>18.50103548653114</v>
       </c>
       <c r="D3" t="n">
-        <v>88.78926237208154</v>
+        <v>67.94184987240051</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.18828424169969</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="C4" t="n">
-        <v>109.9891222975871</v>
+        <v>50.87220253866122</v>
       </c>
       <c r="D4" t="n">
-        <v>177.0699794333632</v>
+        <v>147.0010107476919</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.71231653158924</v>
+        <v>20.42035224833366</v>
       </c>
       <c r="C5" t="n">
-        <v>207.1978529812894</v>
+        <v>155.975166512212</v>
       </c>
       <c r="D5" t="n">
-        <v>136.4383871977005</v>
+        <v>127.4063083186298</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.20132469929539</v>
+        <v>11.91449013873929</v>
       </c>
       <c r="C6" t="n">
-        <v>199.2859482327643</v>
+        <v>212.2469814242307</v>
       </c>
       <c r="D6" t="n">
-        <v>60.13597387593413</v>
+        <v>68.79007988886977</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.204465564390594</v>
+        <v>4.73104218676538</v>
       </c>
       <c r="C7" t="n">
-        <v>157.6215574122339</v>
+        <v>118.874920768725</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>85.11752595819846</v>
+        <v>59.41537106101696</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>33.39218466454675</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.184789552576653</v>
+        <v>0.2100940087088174</v>
       </c>
       <c r="C2" t="n">
-        <v>7.344454575470388</v>
+        <v>2.291399141712055</v>
       </c>
       <c r="D2" t="n">
-        <v>14.78512042595696</v>
+        <v>7.763660845183777</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.91903902436203</v>
+        <v>2.312015843501239</v>
       </c>
       <c r="C3" t="n">
-        <v>18.74156367407161</v>
+        <v>17.04314014572463</v>
       </c>
       <c r="D3" t="n">
-        <v>79.09450379264428</v>
+        <v>59.66080798707867</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.29114676646735</v>
+        <v>11.11632925518663</v>
       </c>
       <c r="C4" t="n">
-        <v>89.95165165390975</v>
+        <v>46.49458952542469</v>
       </c>
       <c r="D4" t="n">
-        <v>179.9415914682851</v>
+        <v>143.2487710220606</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.33973543006097</v>
+        <v>18.75138115111408</v>
       </c>
       <c r="C5" t="n">
-        <v>206.7806102069845</v>
+        <v>113.4654909183251</v>
       </c>
       <c r="D5" t="n">
-        <v>161.6693031968435</v>
+        <v>133.8858431666588</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.54600025894403</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>257.4495909708666</v>
+        <v>192.8859349487794</v>
       </c>
       <c r="D6" t="n">
-        <v>81.91211970383264</v>
+        <v>75.43160310809944</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>215.0528163629681</v>
+        <v>148.9978855781299</v>
       </c>
       <c r="D7" t="n">
-        <v>41.56130731158447</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>134.185276216454</v>
+        <v>66.7588438887831</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>57.46562012038278</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>21.41093568191868</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.34245002233289</v>
+        <v>0.1610066234964769</v>
       </c>
       <c r="C2" t="n">
-        <v>4.854742397500478</v>
+        <v>3.401755795215198</v>
       </c>
       <c r="D2" t="n">
-        <v>12.14912784005428</v>
+        <v>11.33722248864217</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.96045235438964</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C3" t="n">
-        <v>23.53740120931728</v>
+        <v>12.04113559258713</v>
       </c>
       <c r="D3" t="n">
-        <v>74.92698478811657</v>
+        <v>52.02771958655972</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.36022895866312</v>
+        <v>7.517242171417827</v>
       </c>
       <c r="C4" t="n">
-        <v>74.44494666533139</v>
+        <v>44.2611134982632</v>
       </c>
       <c r="D4" t="n">
-        <v>179.4055572217664</v>
+        <v>141.1684476367616</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.07666810305183</v>
+        <v>18.26050729899067</v>
       </c>
       <c r="C5" t="n">
-        <v>196.7422399310609</v>
+        <v>98.78836273983532</v>
       </c>
       <c r="D5" t="n">
-        <v>179.3162181806799</v>
+        <v>155.6315548157257</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.15356321915257</v>
+        <v>19.0390332284584</v>
       </c>
       <c r="C6" t="n">
-        <v>292.6697898607209</v>
+        <v>188.9815243289898</v>
       </c>
       <c r="D6" t="n">
-        <v>96.60397409788615</v>
+        <v>99.26058338557803</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.69029180927252</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>269.1903117659542</v>
+        <v>219.2448790601019</v>
       </c>
       <c r="D7" t="n">
-        <v>46.95110220789945</v>
+        <v>48.56804067679396</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C8" t="n">
-        <v>172.8219571170873</v>
+        <v>136.3549386428395</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>65.23124446097505</v>
+        <v>58.3531200450219</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>28.18597658892593</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>17.94732978133594</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.086614782151972</v>
+        <v>0.5880668748438395</v>
       </c>
       <c r="C2" t="n">
-        <v>7.780350556155972</v>
+        <v>6.608143797285281</v>
       </c>
       <c r="D2" t="n">
-        <v>11.61603883664826</v>
+        <v>14.35609667920111</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.10356653503143</v>
+        <v>0.947386534598172</v>
       </c>
       <c r="C3" t="n">
-        <v>21.22538536581604</v>
+        <v>12.70381529295373</v>
       </c>
       <c r="D3" t="n">
-        <v>69.14449081010285</v>
+        <v>49.07265899677682</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.61700488881928</v>
+        <v>5.028511741152163</v>
       </c>
       <c r="C4" t="n">
-        <v>67.42545057996669</v>
+        <v>36.37375244234432</v>
       </c>
       <c r="D4" t="n">
-        <v>174.2877064395278</v>
+        <v>135.7953424514188</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.83123117699012</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="C5" t="n">
-        <v>171.5604113171301</v>
+        <v>89.6335653977338</v>
       </c>
       <c r="D5" t="n">
-        <v>196.1286476159066</v>
+        <v>170.8977316167635</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.65924540229769</v>
+        <v>22.25916569838794</v>
       </c>
       <c r="C6" t="n">
-        <v>301.4849024971531</v>
+        <v>173.4443851615798</v>
       </c>
       <c r="D6" t="n">
-        <v>119.9901861607494</v>
+        <v>122.3650338573225</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.58398531977338</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="C7" t="n">
-        <v>329.3164681648458</v>
+        <v>249.4876170894249</v>
       </c>
       <c r="D7" t="n">
-        <v>57.85046522044755</v>
+        <v>64.55776553586176</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>243.7532287489193</v>
+        <v>215.7979628704914</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>117.3718650335231</v>
+        <v>113.7109278443868</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>45.98015372839937</v>
+        <v>48.25780840225197</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.546874528994478</v>
+        <v>4.710425484976196</v>
       </c>
       <c r="C2" t="n">
-        <v>6.598326320242812</v>
+        <v>7.333655350723674</v>
       </c>
       <c r="D2" t="n">
-        <v>18.25559856046944</v>
+        <v>10.25926350937917</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.233476027161494</v>
+        <v>0.4692754026299753</v>
       </c>
       <c r="C2" t="n">
-        <v>4.544510122958485</v>
+        <v>5.738315331322607</v>
       </c>
       <c r="D2" t="n">
-        <v>8.642325040484671</v>
+        <v>20.14546289114455</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.98637870532756</v>
+        <v>1.45298660228528</v>
       </c>
       <c r="C3" t="n">
-        <v>26.94406574305371</v>
+        <v>19.45333075965055</v>
       </c>
       <c r="D3" t="n">
-        <v>74.13176914767665</v>
+        <v>48.86158324036376</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.16726662928301</v>
+        <v>3.407646281440679</v>
       </c>
       <c r="C4" t="n">
-        <v>98.60477591914113</v>
+        <v>33.97436105316512</v>
       </c>
       <c r="D4" t="n">
-        <v>180.0692186698372</v>
+        <v>129.0183380490031</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.2447425824605</v>
+        <v>11.83005983617407</v>
       </c>
       <c r="C5" t="n">
-        <v>254.6162670964103</v>
+        <v>77.63169971331654</v>
       </c>
       <c r="D5" t="n">
-        <v>177.7699655464912</v>
+        <v>180.4206843479576</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.35475507859837</v>
+        <v>21.61513920440203</v>
       </c>
       <c r="C6" t="n">
-        <v>273.0269817941507</v>
+        <v>159.5173122291345</v>
       </c>
       <c r="D6" t="n">
-        <v>90.76748399613888</v>
+        <v>143.7789147823539</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>171.3954777028166</v>
+        <v>253.2005869068863</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>82.28420208374216</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>86.45270283597411</v>
+        <v>272.542980175957</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>43.72704274715294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>3.660937189136355</v>
       </c>
       <c r="C9" t="n">
-        <v>35.05624702324509</v>
+        <v>183.823421890877</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>87.40499810909354</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>38.38240824523329</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>19.90198946049134</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.191882770684633</v>
+        <v>3.784637399871454</v>
       </c>
       <c r="C2" t="n">
-        <v>5.868887775987432</v>
+        <v>7.408268176246431</v>
       </c>
       <c r="D2" t="n">
-        <v>22.04907168967911</v>
+        <v>18.16920476249572</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.78588118948296</v>
+        <v>7.780350556155972</v>
       </c>
       <c r="C3" t="n">
-        <v>16.62589737141974</v>
+        <v>14.47586989911922</v>
       </c>
       <c r="D3" t="n">
-        <v>18.47158305540374</v>
+        <v>10.02855279888117</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39678486363605</v>
+        <v>11.67816082422528</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13610899197695</v>
+        <v>59.9478922310231</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576092336898359</v>
+        <v>0.7785440549483519</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.415901173702153</v>
+        <v>3.593196597543326</v>
       </c>
       <c r="C2" t="n">
-        <v>4.675082567623311</v>
+        <v>5.66664774891259</v>
       </c>
       <c r="D2" t="n">
-        <v>22.62437584436775</v>
+        <v>18.68167706411256</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.54874021341174</v>
+        <v>11.22137625954104</v>
       </c>
       <c r="C3" t="n">
-        <v>20.54307071136451</v>
+        <v>24.12154109334413</v>
       </c>
       <c r="D3" t="n">
-        <v>32.52530144169683</v>
+        <v>23.49813130114741</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.74544960715959</v>
+        <v>9.674141877648069</v>
       </c>
       <c r="C4" t="n">
-        <v>25.89555919491812</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D4" t="n">
-        <v>24.74691438094935</v>
+        <v>19.50143639715864</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43753928424102</v>
+        <v>13.62982217724396</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12521916471304</v>
+        <v>73.76139060626141</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25000827036653</v>
+        <v>1.603508491440466</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.713370728088937</v>
+        <v>2.908918447683299</v>
       </c>
       <c r="C2" t="n">
-        <v>9.037969365296137</v>
+        <v>5.01084028247572</v>
       </c>
       <c r="D2" t="n">
-        <v>34.7185258129842</v>
+        <v>16.79868496736717</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.27737693641212</v>
+        <v>12.06077054667207</v>
       </c>
       <c r="C3" t="n">
-        <v>19.1146278016854</v>
+        <v>22.84526907782328</v>
       </c>
       <c r="D3" t="n">
-        <v>43.07418052382881</v>
+        <v>33.51195788446487</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.24466046700248</v>
+        <v>17.03823140720339</v>
       </c>
       <c r="C4" t="n">
-        <v>40.93004353775377</v>
+        <v>46.94128473085699</v>
       </c>
       <c r="D4" t="n">
-        <v>35.46759931132452</v>
+        <v>27.28669569183585</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.10004045484194</v>
+        <v>9.081166264282997</v>
       </c>
       <c r="C5" t="n">
-        <v>29.62423697564751</v>
+        <v>29.10881943091793</v>
       </c>
       <c r="D5" t="n">
-        <v>31.53864499892879</v>
+        <v>26.77716863333176</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>24.20008090968387</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.728789774221</v>
+        <v>14.8421176602295</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0456176227481</v>
+        <v>87.40358177690707</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182197443555249</v>
+        <v>2.473686276704917</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.898741117742336</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C2" t="n">
-        <v>7.073492209098268</v>
+        <v>4.816454237034852</v>
       </c>
       <c r="D2" t="n">
-        <v>33.30186387575606</v>
+        <v>27.85512761259475</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1595672119025</v>
+        <v>10.95139564087317</v>
       </c>
       <c r="C3" t="n">
-        <v>28.31851252899925</v>
+        <v>20.79832511446868</v>
       </c>
       <c r="D3" t="n">
-        <v>59.87679248201297</v>
+        <v>39.17173339944773</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.4098150654942</v>
+        <v>20.90533561423158</v>
       </c>
       <c r="C4" t="n">
-        <v>44.78438502462675</v>
+        <v>53.13120400613313</v>
       </c>
       <c r="D4" t="n">
-        <v>48.34518394792993</v>
+        <v>37.6755498981756</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.98547907308133</v>
+        <v>17.84326452468578</v>
       </c>
       <c r="C5" t="n">
-        <v>54.43791020048565</v>
+        <v>62.53732876052183</v>
       </c>
       <c r="D5" t="n">
-        <v>36.59464567579986</v>
+        <v>30.87596529856219</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.06920536538279</v>
+        <v>8.734609324683873</v>
       </c>
       <c r="C6" t="n">
-        <v>30.10823859384119</v>
+        <v>30.3497485290859</v>
       </c>
       <c r="D6" t="n">
-        <v>38.64158963915446</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.95250056176443</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04964252707871</v>
+        <v>16.08855981138626</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7524298195135</v>
+        <v>101.6119567034922</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016547509026237</v>
+        <v>3.387065223449739</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.404922022506191</v>
+        <v>1.657190124768616</v>
       </c>
       <c r="C2" t="n">
-        <v>6.959609475405639</v>
+        <v>4.73693267299086</v>
       </c>
       <c r="D2" t="n">
-        <v>31.67019919129786</v>
+        <v>39.20413107368788</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.13778883595982</v>
+        <v>8.423395302437633</v>
       </c>
       <c r="C3" t="n">
-        <v>26.10958019444392</v>
+        <v>19.56623174563893</v>
       </c>
       <c r="D3" t="n">
-        <v>67.61296439147783</v>
+        <v>51.62520302781852</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.86253962587222</v>
+        <v>21.00743737547325</v>
       </c>
       <c r="C4" t="n">
-        <v>49.07265899677682</v>
+        <v>52.53135615883833</v>
       </c>
       <c r="D4" t="n">
-        <v>57.99380038526758</v>
+        <v>47.87296330218722</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.59215809657685</v>
+        <v>24.98547907308133</v>
       </c>
       <c r="C5" t="n">
-        <v>51.71356032120075</v>
+        <v>82.14773915285187</v>
       </c>
       <c r="D5" t="n">
-        <v>36.32466505713199</v>
+        <v>37.50276230222816</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.19625172985813</v>
+        <v>16.46292725251477</v>
       </c>
       <c r="C6" t="n">
-        <v>39.7686360036298</v>
+        <v>66.73724543928969</v>
       </c>
       <c r="D6" t="n">
-        <v>32.16107304342126</v>
+        <v>36.26674194258143</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>20.90042687571034</v>
+        <v>31.32069700858599</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052230461610416</v>
+        <v>17.36177985591016</v>
       </c>
       <c r="C21" t="n">
-        <v>66.11466057759765</v>
+        <v>115.4558360418026</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40764403850651</v>
+        <v>4.340444963977539</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.432991795301848</v>
+        <v>3.249584901056942</v>
       </c>
       <c r="C2" t="n">
-        <v>5.936628367580462</v>
+        <v>6.038730128822131</v>
       </c>
       <c r="D2" t="n">
-        <v>32.78939157413922</v>
+        <v>39.32979477983147</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.73942025221387</v>
+        <v>6.999861131279758</v>
       </c>
       <c r="C3" t="n">
-        <v>26.81152980298039</v>
+        <v>18.8691908756237</v>
       </c>
       <c r="D3" t="n">
-        <v>77.87713663937824</v>
+        <v>68.86469271439252</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.01791780505048</v>
+        <v>18.40384246381071</v>
       </c>
       <c r="C4" t="n">
-        <v>59.42322504265093</v>
+        <v>50.08091388903829</v>
       </c>
       <c r="D4" t="n">
-        <v>79.42240752586271</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.95526587842793</v>
+        <v>28.42159603794517</v>
       </c>
       <c r="C5" t="n">
-        <v>75.59457322700442</v>
+        <v>89.85445863118933</v>
       </c>
       <c r="D5" t="n">
-        <v>50.36365722786139</v>
+        <v>45.77398671050754</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.25287430153496</v>
+        <v>24.63401339496097</v>
       </c>
       <c r="C6" t="n">
-        <v>64.76491430145784</v>
+        <v>98.65680854746624</v>
       </c>
       <c r="D6" t="n">
-        <v>36.95102009244145</v>
+        <v>39.88939097125216</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.59992996275281</v>
+        <v>13.95358012045992</v>
       </c>
       <c r="C7" t="n">
-        <v>42.22006002113408</v>
+        <v>63.24026011676253</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>24.11663235482289</v>
+        <v>33.04562772494764</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>43.98720588877834</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.271525211294918</v>
+        <v>18.65502295480246</v>
       </c>
       <c r="C21" t="n">
-        <v>75.44207406718478</v>
+        <v>128.8084918307788</v>
       </c>
       <c r="D21" t="n">
-        <v>5.453643908471189</v>
+        <v>5.330006558514987</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.903829782712818</v>
+        <v>2.813688920371358</v>
       </c>
       <c r="C2" t="n">
-        <v>5.160065933521236</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D2" t="n">
-        <v>32.6735453450381</v>
+        <v>30.78368101436299</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.61531913085127</v>
+        <v>10.91703447122453</v>
       </c>
       <c r="C3" t="n">
-        <v>24.58296251434013</v>
+        <v>29.95312245657018</v>
       </c>
       <c r="D3" t="n">
-        <v>86.04036880019046</v>
+        <v>76.02163347835176</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.5952265128766</v>
+        <v>13.64334784591792</v>
       </c>
       <c r="C4" t="n">
-        <v>63.90293981712914</v>
+        <v>76.5763209312512</v>
       </c>
       <c r="D4" t="n">
-        <v>100.6340484238193</v>
+        <v>57.25356261626548</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.3064127613788</v>
+        <v>13.8671863224862</v>
       </c>
       <c r="C5" t="n">
-        <v>94.07597375945062</v>
+        <v>58.92940594741481</v>
       </c>
       <c r="D5" t="n">
-        <v>67.49515466696822</v>
+        <v>37.45367491701582</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.02773528209295</v>
+        <v>8.654106012935635</v>
       </c>
       <c r="C6" t="n">
-        <v>95.27566945404023</v>
+        <v>41.62021217383928</v>
       </c>
       <c r="D6" t="n">
-        <v>43.9548082145382</v>
+        <v>25.43904651244335</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>70.30688009193108</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>41.39048321104552</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>27.17968519207294</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.47731988187285</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.11984867106956</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.542654896638743</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
